--- a/data/data_raw/eurostat/AT_gas_NRG_CB_GASM.xlsx
+++ b/data/data_raw/eurostat/AT_gas_NRG_CB_GASM.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HG33"/>
+  <dimension ref="A1:HM33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1497,6 +1497,36 @@
       <c r="HG1" s="1" t="inlineStr">
         <is>
           <t>2025-05</t>
+        </is>
+      </c>
+      <c r="HH1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="HI1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="HJ1" s="1" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="HK1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="HL1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="HM1" s="1" t="inlineStr">
+        <is>
+          <t>2025-11</t>
         </is>
       </c>
     </row>
@@ -2012,6 +2042,24 @@
       <c r="HG2" t="n">
         <v>41.452</v>
       </c>
+      <c r="HH2" t="n">
+        <v>38.955</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>44.898</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>41.718</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>40.082</v>
+      </c>
+      <c r="HL2" t="n">
+        <v>38.637</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>39.736</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -2668,6 +2716,24 @@
       </c>
       <c r="HG3" t="n">
         <v>1628.075</v>
+      </c>
+      <c r="HH3" t="n">
+        <v>1529.986</v>
+      </c>
+      <c r="HI3" t="n">
+        <v>1763.42</v>
+      </c>
+      <c r="HJ3" t="n">
+        <v>1638.497</v>
+      </c>
+      <c r="HK3" t="n">
+        <v>1574.244</v>
+      </c>
+      <c r="HL3" t="n">
+        <v>1517.515</v>
+      </c>
+      <c r="HM3" t="n">
+        <v>1560.658</v>
       </c>
     </row>
     <row r="4">
@@ -3038,6 +3104,24 @@
       <c r="HG4" t="n">
         <v>1.175</v>
       </c>
+      <c r="HH4" t="n">
+        <v>1.206</v>
+      </c>
+      <c r="HI4" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="HJ4" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="HK4" t="n">
+        <v>1.397</v>
+      </c>
+      <c r="HL4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="HM4" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -3407,6 +3491,24 @@
       <c r="HG5" t="n">
         <v>46.132</v>
       </c>
+      <c r="HH5" t="n">
+        <v>47.371</v>
+      </c>
+      <c r="HI5" t="n">
+        <v>44.726</v>
+      </c>
+      <c r="HJ5" t="n">
+        <v>48.229</v>
+      </c>
+      <c r="HK5" t="n">
+        <v>54.884</v>
+      </c>
+      <c r="HL5" t="n">
+        <v>60.078</v>
+      </c>
+      <c r="HM5" t="n">
+        <v>51.065</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -3920,6 +4022,24 @@
       <c r="HG6" t="n">
         <v>1489.27</v>
       </c>
+      <c r="HH6" t="n">
+        <v>1901.554</v>
+      </c>
+      <c r="HI6" t="n">
+        <v>1671.012</v>
+      </c>
+      <c r="HJ6" t="n">
+        <v>1660.209</v>
+      </c>
+      <c r="HK6" t="n">
+        <v>1320.656</v>
+      </c>
+      <c r="HL6" t="n">
+        <v>1126.526</v>
+      </c>
+      <c r="HM6" t="n">
+        <v>1142.487</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -4576,6 +4696,24 @@
       </c>
       <c r="HG7" t="n">
         <v>58492.312</v>
+      </c>
+      <c r="HH7" t="n">
+        <v>74685.099</v>
+      </c>
+      <c r="HI7" t="n">
+        <v>65630.408</v>
+      </c>
+      <c r="HJ7" t="n">
+        <v>65206.041</v>
+      </c>
+      <c r="HK7" t="n">
+        <v>51869.864</v>
+      </c>
+      <c r="HL7" t="n">
+        <v>44245.26</v>
+      </c>
+      <c r="HM7" t="n">
+        <v>44872.118</v>
       </c>
     </row>
     <row r="8">
@@ -5090,6 +5228,24 @@
       <c r="HG8" t="n">
         <v>536.1420000000001</v>
       </c>
+      <c r="HH8" t="n">
+        <v>638.823</v>
+      </c>
+      <c r="HI8" t="n">
+        <v>597.782</v>
+      </c>
+      <c r="HJ8" t="n">
+        <v>694.753</v>
+      </c>
+      <c r="HK8" t="n">
+        <v>633.981</v>
+      </c>
+      <c r="HL8" t="n">
+        <v>623.548</v>
+      </c>
+      <c r="HM8" t="n">
+        <v>959.152</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -5746,6 +5902,24 @@
       </c>
       <c r="HG9" t="n">
         <v>21057.465</v>
+      </c>
+      <c r="HH9" t="n">
+        <v>25090.332</v>
+      </c>
+      <c r="HI9" t="n">
+        <v>23478.4</v>
+      </c>
+      <c r="HJ9" t="n">
+        <v>27287.01</v>
+      </c>
+      <c r="HK9" t="n">
+        <v>24900.108</v>
+      </c>
+      <c r="HL9" t="n">
+        <v>24490.394</v>
+      </c>
+      <c r="HM9" t="n">
+        <v>37671.497</v>
       </c>
     </row>
     <row r="10">
@@ -6036,6 +6210,24 @@
       <c r="HG10" t="n">
         <v>0</v>
       </c>
+      <c r="HH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI10" t="n">
+        <v>-16.088</v>
+      </c>
+      <c r="HJ10" t="n">
+        <v>-19.306</v>
+      </c>
+      <c r="HK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL10" t="n">
+        <v>-16.088</v>
+      </c>
+      <c r="HM10" t="n">
+        <v>-45.047</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -6325,6 +6517,24 @@
       <c r="HG11" t="n">
         <v>0</v>
       </c>
+      <c r="HH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI11" t="n">
+        <v>-512.789</v>
+      </c>
+      <c r="HJ11" t="n">
+        <v>-615.347</v>
+      </c>
+      <c r="HK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL11" t="n">
+        <v>-512.789</v>
+      </c>
+      <c r="HM11" t="n">
+        <v>-1435.81</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -6838,6 +7048,24 @@
       <c r="HG12" t="n">
         <v>597.141</v>
       </c>
+      <c r="HH12" t="n">
+        <v>995.85</v>
+      </c>
+      <c r="HI12" t="n">
+        <v>803.46</v>
+      </c>
+      <c r="HJ12" t="n">
+        <v>720.073</v>
+      </c>
+      <c r="HK12" t="n">
+        <v>371.076</v>
+      </c>
+      <c r="HL12" t="n">
+        <v>-114.065</v>
+      </c>
+      <c r="HM12" t="n">
+        <v>-613.913</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -7494,6 +7722,24 @@
       </c>
       <c r="HG13" t="n">
         <v>23453.207</v>
+      </c>
+      <c r="HH13" t="n">
+        <v>39112.836</v>
+      </c>
+      <c r="HI13" t="n">
+        <v>31556.551</v>
+      </c>
+      <c r="HJ13" t="n">
+        <v>28281.468</v>
+      </c>
+      <c r="HK13" t="n">
+        <v>14574.309</v>
+      </c>
+      <c r="HL13" t="n">
+        <v>-4480.001</v>
+      </c>
+      <c r="HM13" t="n">
+        <v>-24111.912</v>
       </c>
     </row>
     <row r="14">
@@ -7840,6 +8086,24 @@
       <c r="HG14" t="n">
         <v>0</v>
       </c>
+      <c r="HH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -8185,6 +8449,24 @@
       <c r="HG15" t="n">
         <v>0</v>
       </c>
+      <c r="HH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -8698,6 +8980,24 @@
       <c r="HG16" t="n">
         <v>411.122</v>
       </c>
+      <c r="HH16" t="n">
+        <v>315.507</v>
+      </c>
+      <c r="HI16" t="n">
+        <v>316.736</v>
+      </c>
+      <c r="HJ16" t="n">
+        <v>293.798</v>
+      </c>
+      <c r="HK16" t="n">
+        <v>350.589</v>
+      </c>
+      <c r="HL16" t="n">
+        <v>652.228</v>
+      </c>
+      <c r="HM16" t="n">
+        <v>856.033</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -9234,6 +9534,24 @@
       </c>
       <c r="HG17" t="n">
         <v>16147.139</v>
+      </c>
+      <c r="HH17" t="n">
+        <v>12391.805</v>
+      </c>
+      <c r="HI17" t="n">
+        <v>12440.088</v>
+      </c>
+      <c r="HJ17" t="n">
+        <v>11539.152</v>
+      </c>
+      <c r="HK17" t="n">
+        <v>13769.668</v>
+      </c>
+      <c r="HL17" t="n">
+        <v>25616.777</v>
+      </c>
+      <c r="HM17" t="n">
+        <v>33621.403</v>
       </c>
     </row>
     <row r="18">
@@ -9748,6 +10066,24 @@
       <c r="HG18" t="n">
         <v>398.614</v>
       </c>
+      <c r="HH18" t="n">
+        <v>307.042</v>
+      </c>
+      <c r="HI18" t="n">
+        <v>331.895</v>
+      </c>
+      <c r="HJ18" t="n">
+        <v>307.635</v>
+      </c>
+      <c r="HK18" t="n">
+        <v>357.078</v>
+      </c>
+      <c r="HL18" t="n">
+        <v>673.298</v>
+      </c>
+      <c r="HM18" t="n">
+        <v>883.331</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -10404,6 +10740,24 @@
       </c>
       <c r="HG19" t="n">
         <v>15655.847</v>
+      </c>
+      <c r="HH19" t="n">
+        <v>12059.288</v>
+      </c>
+      <c r="HI19" t="n">
+        <v>12916.392</v>
+      </c>
+      <c r="HJ19" t="n">
+        <v>11939.636</v>
+      </c>
+      <c r="HK19" t="n">
+        <v>14024.575</v>
+      </c>
+      <c r="HL19" t="n">
+        <v>26325.249</v>
+      </c>
+      <c r="HM19" t="n">
+        <v>34360.066</v>
       </c>
     </row>
     <row r="20">
@@ -10918,6 +11272,24 @@
       <c r="HG20" t="n">
         <v>9.295</v>
       </c>
+      <c r="HH20" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="HI20" t="n">
+        <v>9.901</v>
+      </c>
+      <c r="HJ20" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="HK20" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="HL20" t="n">
+        <v>159.727</v>
+      </c>
+      <c r="HM20" t="n">
+        <v>202.285</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -11502,6 +11874,24 @@
       </c>
       <c r="HG21" t="n">
         <v>365.05</v>
+      </c>
+      <c r="HH21" t="n">
+        <v>302.406</v>
+      </c>
+      <c r="HI21" t="n">
+        <v>388.862</v>
+      </c>
+      <c r="HJ21" t="n">
+        <v>109.784</v>
+      </c>
+      <c r="HK21" t="n">
+        <v>1158.646</v>
+      </c>
+      <c r="HL21" t="n">
+        <v>6273.418</v>
+      </c>
+      <c r="HM21" t="n">
+        <v>7944.895</v>
       </c>
     </row>
     <row r="22">
@@ -12016,6 +12406,24 @@
       <c r="HG22" t="n">
         <v>15.797</v>
       </c>
+      <c r="HH22" t="n">
+        <v>15.912</v>
+      </c>
+      <c r="HI22" t="n">
+        <v>18.212</v>
+      </c>
+      <c r="HJ22" t="n">
+        <v>16.983</v>
+      </c>
+      <c r="HK22" t="n">
+        <v>15.532</v>
+      </c>
+      <c r="HL22" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="HM22" t="n">
+        <v>16.422</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -12672,6 +13080,24 @@
       </c>
       <c r="HG23" t="n">
         <v>620.421</v>
+      </c>
+      <c r="HH23" t="n">
+        <v>624.938</v>
+      </c>
+      <c r="HI23" t="n">
+        <v>715.3099999999999</v>
+      </c>
+      <c r="HJ23" t="n">
+        <v>667.037</v>
+      </c>
+      <c r="HK23" t="n">
+        <v>610.021</v>
+      </c>
+      <c r="HL23" t="n">
+        <v>578.944</v>
+      </c>
+      <c r="HM23" t="n">
+        <v>644.9930000000001</v>
       </c>
     </row>
     <row r="24">
@@ -13018,6 +13444,24 @@
       <c r="HG24" t="n">
         <v>0</v>
       </c>
+      <c r="HH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -13363,6 +13807,24 @@
       <c r="HG25" t="n">
         <v>0</v>
       </c>
+      <c r="HH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -13708,6 +14170,24 @@
       <c r="HG26" t="n">
         <v>0</v>
       </c>
+      <c r="HH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -14051,6 +14531,24 @@
         <v>0</v>
       </c>
       <c r="HG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14294,6 +14792,12 @@
       <c r="HE28" t="inlineStr"/>
       <c r="HF28" t="inlineStr"/>
       <c r="HG28" t="inlineStr"/>
+      <c r="HH28" t="inlineStr"/>
+      <c r="HI28" t="inlineStr"/>
+      <c r="HJ28" t="inlineStr"/>
+      <c r="HK28" t="inlineStr"/>
+      <c r="HL28" t="inlineStr"/>
+      <c r="HM28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -14535,6 +15039,12 @@
       <c r="HE29" t="inlineStr"/>
       <c r="HF29" t="inlineStr"/>
       <c r="HG29" t="inlineStr"/>
+      <c r="HH29" t="inlineStr"/>
+      <c r="HI29" t="inlineStr"/>
+      <c r="HJ29" t="inlineStr"/>
+      <c r="HK29" t="inlineStr"/>
+      <c r="HL29" t="inlineStr"/>
+      <c r="HM29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -14818,6 +15328,24 @@
       <c r="HG30" t="n">
         <v>89.786</v>
       </c>
+      <c r="HH30" t="n">
+        <v>45.615</v>
+      </c>
+      <c r="HI30" t="n">
+        <v>41.826</v>
+      </c>
+      <c r="HJ30" t="n">
+        <v>41.826</v>
+      </c>
+      <c r="HK30" t="n">
+        <v>60.277</v>
+      </c>
+      <c r="HL30" t="n">
+        <v>145.931</v>
+      </c>
+      <c r="HM30" t="n">
+        <v>233.907</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -15101,6 +15629,24 @@
       <c r="HG31" t="n">
         <v>3526.422</v>
       </c>
+      <c r="HH31" t="n">
+        <v>1791.577</v>
+      </c>
+      <c r="HI31" t="n">
+        <v>1642.734</v>
+      </c>
+      <c r="HJ31" t="n">
+        <v>1642.769</v>
+      </c>
+      <c r="HK31" t="n">
+        <v>2367.413</v>
+      </c>
+      <c r="HL31" t="n">
+        <v>5731.557</v>
+      </c>
+      <c r="HM31" t="n">
+        <v>9186.873</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -15470,6 +16016,24 @@
       <c r="HG32" t="n">
         <v>-12.508</v>
       </c>
+      <c r="HH32" t="n">
+        <v>-8.465</v>
+      </c>
+      <c r="HI32" t="n">
+        <v>15.159</v>
+      </c>
+      <c r="HJ32" t="n">
+        <v>13.837</v>
+      </c>
+      <c r="HK32" t="n">
+        <v>6.489</v>
+      </c>
+      <c r="HL32" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="HM32" t="n">
+        <v>27.298</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -15839,6 +16403,24 @@
       <c r="HG33" t="n">
         <v>-491.292</v>
       </c>
+      <c r="HH33" t="n">
+        <v>-332.517</v>
+      </c>
+      <c r="HI33" t="n">
+        <v>476.304</v>
+      </c>
+      <c r="HJ33" t="n">
+        <v>400.484</v>
+      </c>
+      <c r="HK33" t="n">
+        <v>254.907</v>
+      </c>
+      <c r="HL33" t="n">
+        <v>708.472</v>
+      </c>
+      <c r="HM33" t="n">
+        <v>738.663</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
